--- a/data/data_raw/eurostat/AT_coal_NRG_CB_SFFM.xlsx
+++ b/data/data_raw/eurostat/AT_coal_NRG_CB_SFFM.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HG50"/>
+  <dimension ref="A1:HL50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1499,6 +1499,31 @@
           <t>2025-05</t>
         </is>
       </c>
+      <c r="HH1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="HI1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="HJ1" s="1" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="HK1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="HL1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -2150,8 +2175,27 @@
       <c r="HE2" t="n">
         <v>0</v>
       </c>
-      <c r="HF2" t="inlineStr"/>
-      <c r="HG2" t="inlineStr"/>
+      <c r="HF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -2803,8 +2847,27 @@
       <c r="HE3" t="n">
         <v>0</v>
       </c>
-      <c r="HF3" t="inlineStr"/>
-      <c r="HG3" t="inlineStr"/>
+      <c r="HF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -3456,8 +3519,27 @@
       <c r="HE4" t="n">
         <v>162.223</v>
       </c>
-      <c r="HF4" t="inlineStr"/>
-      <c r="HG4" t="inlineStr"/>
+      <c r="HF4" t="n">
+        <v>217.419</v>
+      </c>
+      <c r="HG4" t="n">
+        <v>199.054</v>
+      </c>
+      <c r="HH4" t="n">
+        <v>196.697</v>
+      </c>
+      <c r="HI4" t="n">
+        <v>224.198</v>
+      </c>
+      <c r="HJ4" t="n">
+        <v>223.091</v>
+      </c>
+      <c r="HK4" t="n">
+        <v>223.336</v>
+      </c>
+      <c r="HL4" t="n">
+        <v>183.682</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -3893,8 +3975,27 @@
       <c r="HE5" t="n">
         <v>65.965</v>
       </c>
-      <c r="HF5" t="inlineStr"/>
-      <c r="HG5" t="inlineStr"/>
+      <c r="HF5" t="n">
+        <v>88.40900000000001</v>
+      </c>
+      <c r="HG5" t="n">
+        <v>91.038</v>
+      </c>
+      <c r="HH5" t="n">
+        <v>89.95999999999999</v>
+      </c>
+      <c r="HI5" t="n">
+        <v>102.537</v>
+      </c>
+      <c r="HJ5" t="n">
+        <v>85.03700000000001</v>
+      </c>
+      <c r="HK5" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="HL5" t="n">
+        <v>79.32599999999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -4546,8 +4647,27 @@
       <c r="HE6" t="n">
         <v>0</v>
       </c>
-      <c r="HF6" t="inlineStr"/>
-      <c r="HG6" t="inlineStr"/>
+      <c r="HF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -5199,8 +5319,27 @@
       <c r="HE7" t="n">
         <v>251.012</v>
       </c>
-      <c r="HF7" t="inlineStr"/>
-      <c r="HG7" t="inlineStr"/>
+      <c r="HF7" t="n">
+        <v>208.5</v>
+      </c>
+      <c r="HG7" t="n">
+        <v>235.425</v>
+      </c>
+      <c r="HH7" t="n">
+        <v>221.702</v>
+      </c>
+      <c r="HI7" t="n">
+        <v>230.694</v>
+      </c>
+      <c r="HJ7" t="n">
+        <v>254.003</v>
+      </c>
+      <c r="HK7" t="n">
+        <v>265.891</v>
+      </c>
+      <c r="HL7" t="n">
+        <v>291.567</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -5852,8 +5991,27 @@
       <c r="HE8" t="n">
         <v>208.5</v>
       </c>
-      <c r="HF8" t="inlineStr"/>
-      <c r="HG8" t="inlineStr"/>
+      <c r="HF8" t="n">
+        <v>235.425</v>
+      </c>
+      <c r="HG8" t="n">
+        <v>221.702</v>
+      </c>
+      <c r="HH8" t="n">
+        <v>230.694</v>
+      </c>
+      <c r="HI8" t="n">
+        <v>254.003</v>
+      </c>
+      <c r="HJ8" t="n">
+        <v>265.891</v>
+      </c>
+      <c r="HK8" t="n">
+        <v>291.567</v>
+      </c>
+      <c r="HL8" t="n">
+        <v>262.673</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -6505,8 +6663,27 @@
       <c r="HE9" t="n">
         <v>42.511</v>
       </c>
-      <c r="HF9" t="inlineStr"/>
-      <c r="HG9" t="inlineStr"/>
+      <c r="HF9" t="n">
+        <v>-26.925</v>
+      </c>
+      <c r="HG9" t="n">
+        <v>13.724</v>
+      </c>
+      <c r="HH9" t="n">
+        <v>-8.992000000000001</v>
+      </c>
+      <c r="HI9" t="n">
+        <v>-23.309</v>
+      </c>
+      <c r="HJ9" t="n">
+        <v>-11.888</v>
+      </c>
+      <c r="HK9" t="n">
+        <v>-25.676</v>
+      </c>
+      <c r="HL9" t="n">
+        <v>28.894</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -7158,8 +7335,27 @@
       <c r="HE10" t="n">
         <v>204.735</v>
       </c>
-      <c r="HF10" t="inlineStr"/>
-      <c r="HG10" t="inlineStr"/>
+      <c r="HF10" t="n">
+        <v>190.494</v>
+      </c>
+      <c r="HG10" t="n">
+        <v>212.778</v>
+      </c>
+      <c r="HH10" t="n">
+        <v>187.705</v>
+      </c>
+      <c r="HI10" t="n">
+        <v>200.889</v>
+      </c>
+      <c r="HJ10" t="n">
+        <v>211.203</v>
+      </c>
+      <c r="HK10" t="n">
+        <v>197.66</v>
+      </c>
+      <c r="HL10" t="n">
+        <v>212.576</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -7595,8 +7791,27 @@
       <c r="HE11" t="n">
         <v>205.052</v>
       </c>
-      <c r="HF11" t="inlineStr"/>
-      <c r="HG11" t="inlineStr"/>
+      <c r="HF11" t="n">
+        <v>188.211</v>
+      </c>
+      <c r="HG11" t="n">
+        <v>209.332</v>
+      </c>
+      <c r="HH11" t="n">
+        <v>187.707</v>
+      </c>
+      <c r="HI11" t="n">
+        <v>199.557</v>
+      </c>
+      <c r="HJ11" t="n">
+        <v>210.81</v>
+      </c>
+      <c r="HK11" t="n">
+        <v>196.219</v>
+      </c>
+      <c r="HL11" t="n">
+        <v>211.103</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -8248,8 +8463,27 @@
       <c r="HE12" t="n">
         <v>0</v>
       </c>
-      <c r="HF12" t="inlineStr"/>
-      <c r="HG12" t="inlineStr"/>
+      <c r="HF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -8901,8 +9135,27 @@
       <c r="HE13" t="n">
         <v>146.142</v>
       </c>
-      <c r="HF13" t="inlineStr"/>
-      <c r="HG13" t="inlineStr"/>
+      <c r="HF13" t="n">
+        <v>140.275</v>
+      </c>
+      <c r="HG13" t="n">
+        <v>145.419</v>
+      </c>
+      <c r="HH13" t="n">
+        <v>136.014</v>
+      </c>
+      <c r="HI13" t="n">
+        <v>144.629</v>
+      </c>
+      <c r="HJ13" t="n">
+        <v>144.962</v>
+      </c>
+      <c r="HK13" t="n">
+        <v>141.273</v>
+      </c>
+      <c r="HL13" t="n">
+        <v>143.837</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -9554,8 +9807,27 @@
       <c r="HE14" t="n">
         <v>57.91</v>
       </c>
-      <c r="HF14" t="inlineStr"/>
-      <c r="HG14" t="inlineStr"/>
+      <c r="HF14" t="n">
+        <v>46.936</v>
+      </c>
+      <c r="HG14" t="n">
+        <v>62.913</v>
+      </c>
+      <c r="HH14" t="n">
+        <v>51.493</v>
+      </c>
+      <c r="HI14" t="n">
+        <v>54.728</v>
+      </c>
+      <c r="HJ14" t="n">
+        <v>65.648</v>
+      </c>
+      <c r="HK14" t="n">
+        <v>54.746</v>
+      </c>
+      <c r="HL14" t="n">
+        <v>67.065</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -9991,8 +10263,27 @@
       <c r="HE15" t="n">
         <v>57.91</v>
       </c>
-      <c r="HF15" t="inlineStr"/>
-      <c r="HG15" t="inlineStr"/>
+      <c r="HF15" t="n">
+        <v>46.936</v>
+      </c>
+      <c r="HG15" t="n">
+        <v>62.913</v>
+      </c>
+      <c r="HH15" t="n">
+        <v>51.493</v>
+      </c>
+      <c r="HI15" t="n">
+        <v>54.728</v>
+      </c>
+      <c r="HJ15" t="n">
+        <v>65.648</v>
+      </c>
+      <c r="HK15" t="n">
+        <v>54.746</v>
+      </c>
+      <c r="HL15" t="n">
+        <v>67.065</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -10644,8 +10935,27 @@
       <c r="HE16" t="n">
         <v>1</v>
       </c>
-      <c r="HF16" t="inlineStr"/>
-      <c r="HG16" t="inlineStr"/>
+      <c r="HF16" t="n">
+        <v>1</v>
+      </c>
+      <c r="HG16" t="n">
+        <v>1</v>
+      </c>
+      <c r="HH16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="HI16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="HJ16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="HK16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="HL16" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -11081,8 +11391,27 @@
       <c r="HE17" t="n">
         <v>-0.318</v>
       </c>
-      <c r="HF17" t="inlineStr"/>
-      <c r="HG17" t="inlineStr"/>
+      <c r="HF17" t="n">
+        <v>2.283</v>
+      </c>
+      <c r="HG17" t="n">
+        <v>3.445</v>
+      </c>
+      <c r="HH17" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="HI17" t="n">
+        <v>1.332</v>
+      </c>
+      <c r="HJ17" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="HK17" t="n">
+        <v>1.441</v>
+      </c>
+      <c r="HL17" t="n">
+        <v>1.473</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -11734,8 +12063,27 @@
       <c r="HE18" t="n">
         <v>0</v>
       </c>
-      <c r="HF18" t="inlineStr"/>
-      <c r="HG18" t="inlineStr"/>
+      <c r="HF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -12387,8 +12735,27 @@
       <c r="HE19" t="n">
         <v>1.052</v>
       </c>
-      <c r="HF19" t="inlineStr"/>
-      <c r="HG19" t="inlineStr"/>
+      <c r="HF19" t="n">
+        <v>3.522</v>
+      </c>
+      <c r="HG19" t="n">
+        <v>5.192</v>
+      </c>
+      <c r="HH19" t="n">
+        <v>5.656</v>
+      </c>
+      <c r="HI19" t="n">
+        <v>3.138</v>
+      </c>
+      <c r="HJ19" t="n">
+        <v>4.318</v>
+      </c>
+      <c r="HK19" t="n">
+        <v>3.203</v>
+      </c>
+      <c r="HL19" t="n">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -13040,8 +13407,27 @@
       <c r="HE20" t="n">
         <v>0</v>
       </c>
-      <c r="HF20" t="inlineStr"/>
-      <c r="HG20" t="inlineStr"/>
+      <c r="HF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -13693,8 +14079,27 @@
       <c r="HE21" t="n">
         <v>0</v>
       </c>
-      <c r="HF21" t="inlineStr"/>
-      <c r="HG21" t="inlineStr"/>
+      <c r="HF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -14346,8 +14751,27 @@
       <c r="HE22" t="n">
         <v>0</v>
       </c>
-      <c r="HF22" t="inlineStr"/>
-      <c r="HG22" t="inlineStr"/>
+      <c r="HF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -14999,8 +15423,27 @@
       <c r="HE23" t="n">
         <v>0</v>
       </c>
-      <c r="HF23" t="inlineStr"/>
-      <c r="HG23" t="inlineStr"/>
+      <c r="HF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -15652,8 +16095,27 @@
       <c r="HE24" t="n">
         <v>1.052</v>
       </c>
-      <c r="HF24" t="inlineStr"/>
-      <c r="HG24" t="inlineStr"/>
+      <c r="HF24" t="n">
+        <v>3.522</v>
+      </c>
+      <c r="HG24" t="n">
+        <v>5.192</v>
+      </c>
+      <c r="HH24" t="n">
+        <v>5.656</v>
+      </c>
+      <c r="HI24" t="n">
+        <v>3.138</v>
+      </c>
+      <c r="HJ24" t="n">
+        <v>4.318</v>
+      </c>
+      <c r="HK24" t="n">
+        <v>3.203</v>
+      </c>
+      <c r="HL24" t="n">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -16305,8 +16767,27 @@
       <c r="HE25" t="n">
         <v>0</v>
       </c>
-      <c r="HF25" t="inlineStr"/>
-      <c r="HG25" t="inlineStr"/>
+      <c r="HF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -16958,8 +17439,27 @@
       <c r="HE26" t="n">
         <v>108.518</v>
       </c>
-      <c r="HF26" t="inlineStr"/>
-      <c r="HG26" t="inlineStr"/>
+      <c r="HF26" t="n">
+        <v>101.071</v>
+      </c>
+      <c r="HG26" t="n">
+        <v>108.406</v>
+      </c>
+      <c r="HH26" t="n">
+        <v>99.15900000000001</v>
+      </c>
+      <c r="HI26" t="n">
+        <v>105.185</v>
+      </c>
+      <c r="HJ26" t="n">
+        <v>104.216</v>
+      </c>
+      <c r="HK26" t="n">
+        <v>101.461</v>
+      </c>
+      <c r="HL26" t="n">
+        <v>106.083</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -17611,8 +18111,27 @@
       <c r="HE27" t="n">
         <v>91.952</v>
       </c>
-      <c r="HF27" t="inlineStr"/>
-      <c r="HG27" t="inlineStr"/>
+      <c r="HF27" t="n">
+        <v>93.241</v>
+      </c>
+      <c r="HG27" t="n">
+        <v>91.13500000000001</v>
+      </c>
+      <c r="HH27" t="n">
+        <v>85.749</v>
+      </c>
+      <c r="HI27" t="n">
+        <v>81.756</v>
+      </c>
+      <c r="HJ27" t="n">
+        <v>96.726</v>
+      </c>
+      <c r="HK27" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="HL27" t="n">
+        <v>87.958</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -18048,8 +18567,27 @@
       <c r="HE28" t="n">
         <v>0</v>
       </c>
-      <c r="HF28" t="inlineStr"/>
-      <c r="HG28" t="inlineStr"/>
+      <c r="HF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -18701,8 +19239,27 @@
       <c r="HE29" t="n">
         <v>0</v>
       </c>
-      <c r="HF29" t="inlineStr"/>
-      <c r="HG29" t="inlineStr"/>
+      <c r="HF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -19354,8 +19911,27 @@
       <c r="HE30" t="n">
         <v>67.02</v>
       </c>
-      <c r="HF30" t="inlineStr"/>
-      <c r="HG30" t="inlineStr"/>
+      <c r="HF30" t="n">
+        <v>70.893</v>
+      </c>
+      <c r="HG30" t="n">
+        <v>75.435</v>
+      </c>
+      <c r="HH30" t="n">
+        <v>72.786</v>
+      </c>
+      <c r="HI30" t="n">
+        <v>75.35299999999999</v>
+      </c>
+      <c r="HJ30" t="n">
+        <v>65.111</v>
+      </c>
+      <c r="HK30" t="n">
+        <v>65.33199999999999</v>
+      </c>
+      <c r="HL30" t="n">
+        <v>60.861</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -20007,8 +20583,27 @@
       <c r="HE31" t="n">
         <v>70.893</v>
       </c>
-      <c r="HF31" t="inlineStr"/>
-      <c r="HG31" t="inlineStr"/>
+      <c r="HF31" t="n">
+        <v>75.435</v>
+      </c>
+      <c r="HG31" t="n">
+        <v>72.786</v>
+      </c>
+      <c r="HH31" t="n">
+        <v>75.35299999999999</v>
+      </c>
+      <c r="HI31" t="n">
+        <v>65.111</v>
+      </c>
+      <c r="HJ31" t="n">
+        <v>65.33199999999999</v>
+      </c>
+      <c r="HK31" t="n">
+        <v>60.861</v>
+      </c>
+      <c r="HL31" t="n">
+        <v>48.516</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -20660,8 +21255,27 @@
       <c r="HE32" t="n">
         <v>-3.873</v>
       </c>
-      <c r="HF32" t="inlineStr"/>
-      <c r="HG32" t="inlineStr"/>
+      <c r="HF32" t="n">
+        <v>-4.542</v>
+      </c>
+      <c r="HG32" t="n">
+        <v>2.649</v>
+      </c>
+      <c r="HH32" t="n">
+        <v>-2.567</v>
+      </c>
+      <c r="HI32" t="n">
+        <v>10.243</v>
+      </c>
+      <c r="HJ32" t="n">
+        <v>-0.221</v>
+      </c>
+      <c r="HK32" t="n">
+        <v>4.471</v>
+      </c>
+      <c r="HL32" t="n">
+        <v>12.345</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -21313,8 +21927,27 @@
       <c r="HE33" t="n">
         <v>196.597</v>
       </c>
-      <c r="HF33" t="inlineStr"/>
-      <c r="HG33" t="inlineStr"/>
+      <c r="HF33" t="n">
+        <v>189.77</v>
+      </c>
+      <c r="HG33" t="n">
+        <v>202.19</v>
+      </c>
+      <c r="HH33" t="n">
+        <v>182.341</v>
+      </c>
+      <c r="HI33" t="n">
+        <v>197.184</v>
+      </c>
+      <c r="HJ33" t="n">
+        <v>200.72</v>
+      </c>
+      <c r="HK33" t="n">
+        <v>190.132</v>
+      </c>
+      <c r="HL33" t="n">
+        <v>206.386</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -21966,8 +22599,27 @@
       <c r="HE34" t="n">
         <v>189.257</v>
       </c>
-      <c r="HF34" t="inlineStr"/>
-      <c r="HG34" t="inlineStr"/>
+      <c r="HF34" t="n">
+        <v>182.708</v>
+      </c>
+      <c r="HG34" t="n">
+        <v>197.821</v>
+      </c>
+      <c r="HH34" t="n">
+        <v>177.951</v>
+      </c>
+      <c r="HI34" t="n">
+        <v>192.379</v>
+      </c>
+      <c r="HJ34" t="n">
+        <v>196.249</v>
+      </c>
+      <c r="HK34" t="n">
+        <v>185.887</v>
+      </c>
+      <c r="HL34" t="n">
+        <v>200.339</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -22619,8 +23271,27 @@
       <c r="HE35" t="n">
         <v>0</v>
       </c>
-      <c r="HF35" t="inlineStr"/>
-      <c r="HG35" t="inlineStr"/>
+      <c r="HF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -23272,8 +23943,27 @@
       <c r="HE36" t="n">
         <v>0</v>
       </c>
-      <c r="HF36" t="inlineStr"/>
-      <c r="HG36" t="inlineStr"/>
+      <c r="HF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -23925,8 +24615,27 @@
       <c r="HE37" t="n">
         <v>0</v>
       </c>
-      <c r="HF37" t="inlineStr"/>
-      <c r="HG37" t="inlineStr"/>
+      <c r="HF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -24382,6 +25091,11 @@
       <c r="HE38" t="inlineStr"/>
       <c r="HF38" t="inlineStr"/>
       <c r="HG38" t="inlineStr"/>
+      <c r="HH38" t="inlineStr"/>
+      <c r="HI38" t="inlineStr"/>
+      <c r="HJ38" t="inlineStr"/>
+      <c r="HK38" t="inlineStr"/>
+      <c r="HL38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -24837,6 +25551,11 @@
       <c r="HE39" t="inlineStr"/>
       <c r="HF39" t="inlineStr"/>
       <c r="HG39" t="inlineStr"/>
+      <c r="HH39" t="inlineStr"/>
+      <c r="HI39" t="inlineStr"/>
+      <c r="HJ39" t="inlineStr"/>
+      <c r="HK39" t="inlineStr"/>
+      <c r="HL39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -25488,8 +26207,27 @@
       <c r="HE40" t="n">
         <v>0</v>
       </c>
-      <c r="HF40" t="inlineStr"/>
-      <c r="HG40" t="inlineStr"/>
+      <c r="HF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -26141,8 +26879,27 @@
       <c r="HE41" t="n">
         <v>0</v>
       </c>
-      <c r="HF41" t="inlineStr"/>
-      <c r="HG41" t="inlineStr"/>
+      <c r="HF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -26794,8 +27551,27 @@
       <c r="HE42" t="n">
         <v>0</v>
       </c>
-      <c r="HF42" t="inlineStr"/>
-      <c r="HG42" t="inlineStr"/>
+      <c r="HF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -27231,8 +28007,27 @@
       <c r="HE43" t="n">
         <v>0</v>
       </c>
-      <c r="HF43" t="inlineStr"/>
-      <c r="HG43" t="inlineStr"/>
+      <c r="HF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -27668,8 +28463,27 @@
       <c r="HE44" t="n">
         <v>0</v>
       </c>
-      <c r="HF44" t="inlineStr"/>
-      <c r="HG44" t="inlineStr"/>
+      <c r="HF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -28105,8 +28919,27 @@
       <c r="HE45" t="n">
         <v>0</v>
       </c>
-      <c r="HF45" t="inlineStr"/>
-      <c r="HG45" t="inlineStr"/>
+      <c r="HF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -28542,8 +29375,27 @@
       <c r="HE46" t="n">
         <v>0</v>
       </c>
-      <c r="HF46" t="inlineStr"/>
-      <c r="HG46" t="inlineStr"/>
+      <c r="HF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -28979,8 +29831,27 @@
       <c r="HE47" t="n">
         <v>0</v>
       </c>
-      <c r="HF47" t="inlineStr"/>
-      <c r="HG47" t="inlineStr"/>
+      <c r="HF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -29416,8 +30287,27 @@
       <c r="HE48" t="n">
         <v>0</v>
       </c>
-      <c r="HF48" t="inlineStr"/>
-      <c r="HG48" t="inlineStr"/>
+      <c r="HF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -29853,8 +30743,27 @@
       <c r="HE49" t="n">
         <v>0</v>
       </c>
-      <c r="HF49" t="inlineStr"/>
-      <c r="HG49" t="inlineStr"/>
+      <c r="HF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -30290,8 +31199,27 @@
       <c r="HE50" t="n">
         <v>0</v>
       </c>
-      <c r="HF50" t="inlineStr"/>
-      <c r="HG50" t="inlineStr"/>
+      <c r="HF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL50" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
